--- a/research/traditional_assets/database/data/south_africa/south_africa_household_products.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_household_products.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.47</v>
+        <v>-1.41</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,61 +612,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.005</v>
+        <v>0.297</v>
       </c>
       <c r="V2">
-        <v>0.005694760820045558</v>
+        <v>0.5881188118811881</v>
       </c>
       <c r="W2">
-        <v>-0.2186046511627907</v>
+        <v>-0.6878048780487805</v>
       </c>
       <c r="X2">
-        <v>0.09775968728337119</v>
+        <v>0.1455367284479568</v>
       </c>
       <c r="Y2">
-        <v>-0.3163643384461619</v>
+        <v>-0.8333416064967374</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>-0.04131868131868132</v>
       </c>
       <c r="AB2">
-        <v>0.08592180523653585</v>
+        <v>0.1455367284479568</v>
       </c>
       <c r="AC2">
-        <v>-0.08592180523653585</v>
+        <v>-0.1868554097666382</v>
       </c>
       <c r="AD2">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.225</v>
+        <v>-0.297</v>
       </c>
       <c r="AH2">
-        <v>0.2075812274368231</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.1008771929824561</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.2039891205802357</v>
+        <v>-1.427884615384615</v>
       </c>
       <c r="AK2">
-        <v>0.09890109890109891</v>
+        <v>-8.999999999999991</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.005</v>
+      </c>
+      <c r="AQ2">
+        <v>18.8</v>
       </c>
     </row>
     <row r="3">
@@ -677,7 +680,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Imbalie Beauty Limited (JSE:ILE)</t>
+          <t>Buka Investments Limited (JSE:BKI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +689,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.47</v>
+        <v>-1.41</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -710,61 +713,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.005</v>
+        <v>0.297</v>
       </c>
       <c r="V3">
-        <v>0.005694760820045558</v>
+        <v>0.5881188118811881</v>
       </c>
       <c r="W3">
-        <v>-0.2186046511627907</v>
+        <v>-0.6878048780487805</v>
       </c>
       <c r="X3">
-        <v>0.09775968728337119</v>
+        <v>0.1455367284479568</v>
       </c>
       <c r="Y3">
-        <v>-0.3163643384461619</v>
+        <v>-0.8333416064967374</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>-0.04131868131868132</v>
       </c>
       <c r="AB3">
-        <v>0.08592180523653585</v>
+        <v>0.1455367284479568</v>
       </c>
       <c r="AC3">
-        <v>-0.08592180523653585</v>
+        <v>-0.1868554097666382</v>
       </c>
       <c r="AD3">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.225</v>
+        <v>-0.297</v>
       </c>
       <c r="AH3">
-        <v>0.2075812274368231</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1008771929824561</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.2039891205802357</v>
+        <v>-1.427884615384615</v>
       </c>
       <c r="AK3">
-        <v>0.09890109890109891</v>
+        <v>-8.999999999999991</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.005</v>
+      </c>
+      <c r="AQ3">
+        <v>18.8</v>
       </c>
     </row>
   </sheetData>
